--- a/excel_templates/公告表.xlsx
+++ b/excel_templates/公告表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -536,12 +536,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>按时归还</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>打发打发打发斯蒂芬</t>
+          <t>借用设备请按时归还</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -569,7 +569,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-02-13 17:24:22</t>
+          <t>2026-02-24 11:20:51</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -584,12 +584,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1231231</t>
+          <t>爱惜设备</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>阿道夫搜嘎哈地方哈哥</t>
+          <t>请自觉维护设备</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -603,24 +603,216 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-02-13 17:36:32</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:20:21</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>29d5b592-bbf5-4226-b59b-3d549febadd1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>借用设备说明</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>需要点击“我要借用”才能看到柜号</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-02-13 17:36:32</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-02-13 17:36:32</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:23:53</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:23:53</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>641a60dd-bc58-4831-b446-bcf107a7d536</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>设备状态</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>请及时修改设备使用状态</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:24:31</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-02-24 14:53:18</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>49403e17-22c7-4cfa-a657-1576dc439716</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>温馨提示</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>每个人借用上限为10台，请及时归还后再借用，逾期超过3天需要先归还再借用</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-02-24 13:52:40</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-02-24 14:52:52</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>56d4a30f-affb-4849-bed3-39d1da2617f4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>查找设备</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>在搜索框输入设备名称</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-02-24 14:42:14</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-02-24 14:53:18</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>0</v>
       </c>
     </row>

--- a/excel_templates/公告表.xlsx
+++ b/excel_templates/公告表.xlsx
@@ -521,11 +521,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-02-13 17:59:50</t>
+          <t>2026-02-25 09:34:54</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
